--- a/esyluban/examples/dev/DataTables/test/test_range.xlsx
+++ b/esyluban/examples/dev/DataTables/test/test_range.xlsx
@@ -417,7 +417,7 @@
       </c>
       <c r="B1" s="0" t="inlineStr">
         <is>
-          <t>full_name="test.TbTestRange" &amp; value_type="test.TestRange" &amp; read_schema_from_file="false" &amp; input="test/test_range.xlsx" &amp; output="test_tbtestrange"</t>
+          <t>full_name="test.TbTestRange" &amp; input="test/test_range.xlsx"</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="0" t="inlineStr">
         <is>
           <t>##group</t>
         </is>
